--- a/data_raw/data_raw_2024_sheets/LTER2_BR_P04_P05_2024.xlsx
+++ b/data_raw/data_raw_2024_sheets/LTER2_BR_P04_P05_2024.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/HLenihan 1/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryananderson/Reference/Bren/Coral Demography/data_raw/data_raw_2024_sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCAB8EF7-1C76-384A-97B8-A5D393441CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E22585F-D5D7-B344-91AE-1D1F07F0B840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1580" yWindow="500" windowWidth="33880" windowHeight="23500" xr2:uid="{9708C3EC-C9CC-4E42-B765-545CAA600A29}"/>
+    <workbookView xWindow="0" yWindow="560" windowWidth="29920" windowHeight="18780" xr2:uid="{9708C3EC-C9CC-4E42-B765-545CAA600A29}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$47</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="30">
   <si>
     <t>LTER2</t>
   </si>
@@ -190,7 +190,42 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF49900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <sz val="11"/>
@@ -199,7 +234,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF159FEC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -211,7 +246,19 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
+          <bgColor rgb="FF17A43F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF006400"/>
         </patternFill>
       </fill>
     </dxf>
@@ -223,7 +270,19 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFB0006"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFA52A2A"/>
         </patternFill>
       </fill>
     </dxf>
@@ -235,7 +294,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
+          <bgColor rgb="FFA1BCD6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -247,7 +306,33 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFB07EDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4A6FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF49900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -259,7 +344,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -271,7 +356,21 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFA500"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF49900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -283,42 +382,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF49900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -330,143 +394,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FF159FEC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF17A43F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF006400"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFB0006"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFA52A2A"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFA1BCD6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFB07EDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD4A6FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF49900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF49900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -800,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD7E96A-BBA2-CD46-888A-2F47089A66EE}">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.1640625" customWidth="1"/>
@@ -1338,18 +1266,103 @@
         <v>8</v>
       </c>
     </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>1.8</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18">
+        <v>2.85</v>
+      </c>
+      <c r="F18">
+        <v>85</v>
+      </c>
+      <c r="G18">
+        <v>30</v>
+      </c>
+      <c r="H18" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="4">
-        <v>45573</v>
-      </c>
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" t="s">
-        <v>29</v>
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>3.55</v>
+      </c>
+      <c r="F19">
+        <v>60</v>
+      </c>
+      <c r="G19">
+        <v>60</v>
+      </c>
+      <c r="H19" t="s">
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <v>20</v>
+      </c>
+      <c r="J19">
+        <v>16</v>
+      </c>
+      <c r="K19">
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -1363,19 +1376,19 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="F20">
         <v>10</v>
       </c>
       <c r="G20">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L20" t="s">
         <v>25</v>
@@ -1395,16 +1408,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>2.85</v>
+        <v>4.09</v>
       </c>
       <c r="F21">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="G21">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1430,25 +1443,22 @@
         <v>3</v>
       </c>
       <c r="E22">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="F22">
         <v>60</v>
       </c>
       <c r="G22">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="H22" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22">
-        <v>20</v>
-      </c>
-      <c r="J22">
-        <v>16</v>
-      </c>
-      <c r="K22">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="L22" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
@@ -1462,19 +1472,19 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G23">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="H23" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L23" t="s">
         <v>25</v>
@@ -1497,13 +1507,13 @@
         <v>3</v>
       </c>
       <c r="E24">
-        <v>4.09</v>
+        <v>7.1</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G24">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1529,13 +1539,13 @@
         <v>3</v>
       </c>
       <c r="E25">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="F25">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1561,13 +1571,13 @@
         <v>3</v>
       </c>
       <c r="E26">
-        <v>6.6</v>
+        <v>7.29</v>
       </c>
       <c r="F26">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="G26">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1593,13 +1603,13 @@
         <v>3</v>
       </c>
       <c r="E27">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="F27">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G27">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1625,13 +1635,13 @@
         <v>3</v>
       </c>
       <c r="E28">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="F28">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G28">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1654,25 +1664,28 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E29">
-        <v>7.29</v>
+        <v>7.6</v>
       </c>
       <c r="F29">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="G29">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
       </c>
-      <c r="L29" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" t="s">
-        <v>27</v>
+      <c r="I29">
+        <v>15</v>
+      </c>
+      <c r="J29">
+        <v>15</v>
+      </c>
+      <c r="K29">
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
@@ -1689,13 +1702,13 @@
         <v>3</v>
       </c>
       <c r="E30">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="F30">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G30">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1715,28 +1728,31 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E31">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="F31">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G31">
-        <v>80</v>
-      </c>
-      <c r="H31" t="s">
-        <v>8</v>
+        <v>60</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M31" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
@@ -1747,34 +1763,34 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
       </c>
       <c r="E32">
-        <v>7.6</v>
+        <v>0.45</v>
       </c>
       <c r="F32">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G32">
-        <v>10</v>
-      </c>
-      <c r="H32" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I32">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J32">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K32">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="L32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>0</v>
       </c>
@@ -1782,31 +1798,34 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E33">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="F33">
         <v>50</v>
       </c>
       <c r="G33">
-        <v>50</v>
-      </c>
-      <c r="H33" t="s">
-        <v>8</v>
+        <v>20</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
       </c>
       <c r="L33" t="s">
-        <v>25</v>
-      </c>
-      <c r="M33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -1820,13 +1839,13 @@
         <v>7</v>
       </c>
       <c r="E34">
-        <v>8.9</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="F34">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G34">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I34">
         <v>1</v>
@@ -1841,209 +1860,80 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>2</v>
-      </c>
-      <c r="D35" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35">
-        <v>0.45</v>
-      </c>
-      <c r="F35">
-        <v>40</v>
-      </c>
-      <c r="G35">
-        <v>20</v>
-      </c>
-      <c r="I35">
-        <v>1</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-      <c r="K35">
-        <v>1</v>
-      </c>
-      <c r="L35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D36" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36">
-        <v>0.5</v>
-      </c>
-      <c r="F36">
-        <v>50</v>
-      </c>
-      <c r="G36">
-        <v>20</v>
-      </c>
-      <c r="I36">
-        <v>1</v>
-      </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
-      <c r="K36">
-        <v>1</v>
-      </c>
-      <c r="L36" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>2</v>
-      </c>
-      <c r="D37" t="s">
-        <v>7</v>
-      </c>
-      <c r="E37">
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="F37">
-        <v>55</v>
-      </c>
-      <c r="G37">
-        <v>30</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-      <c r="J37">
-        <v>1</v>
-      </c>
-      <c r="K37">
-        <v>1</v>
-      </c>
-      <c r="L37" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="A31:G34">
+    <cfRule type="expression" dxfId="20" priority="1">
+      <formula>A31="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>A31="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A2:H2">
-    <cfRule type="beginsWith" dxfId="26" priority="16" operator="beginsWith" text="FI">
+    <cfRule type="beginsWith" dxfId="18" priority="16" operator="beginsWith" text="FI">
       <formula>LEFT(A2,LEN("FI"))="FI"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="17" operator="containsText" text="Missing data">
+    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="Missing data">
       <formula>NOT(ISERROR(SEARCH("Missing data",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:K4 I14:K14 I22:K22 I32:K32 D34:G37 I35:K37 A3:H18 A20:H33 H19">
-    <cfRule type="expression" dxfId="24" priority="18">
+  <conditionalFormatting sqref="I4:K4 I14:K14 A3:H30 I19:K19 I29:K29 I32:K34">
+    <cfRule type="expression" dxfId="16" priority="18">
       <formula>A3="UK"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="19">
+    <cfRule type="expression" dxfId="15" priority="19">
       <formula>A3="Na"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:M2">
-    <cfRule type="beginsWith" dxfId="22" priority="9" operator="beginsWith" text="UK">
+    <cfRule type="beginsWith" dxfId="14" priority="9" operator="beginsWith" text="UK">
       <formula>LEFT(A2,LEN("UK"))="UK"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="21" priority="15" operator="beginsWith" text="FU">
+    <cfRule type="beginsWith" dxfId="13" priority="15" operator="beginsWith" text="FU">
       <formula>LEFT(A2,LEN("FU"))="FU"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H33 I4:K4 I14:K14 I22:K22 I32:K32">
-    <cfRule type="containsText" dxfId="20" priority="20" operator="containsText" text=",">
+  <conditionalFormatting sqref="I4:K4 I14:K14 I19:K19 I29:K29 H3:H30">
+    <cfRule type="containsText" dxfId="12" priority="20" operator="containsText" text=",">
       <formula>NOT(ISERROR(SEARCH(",", H3)))</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="19" priority="21" operator="beginsWith" text="Fusion">
+    <cfRule type="beginsWith" dxfId="11" priority="21" operator="beginsWith" text="Fusion">
       <formula>LEFT(H3,LEN("Fusion"))="Fusion"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="18" priority="22" operator="beginsWith" text="Fission">
+    <cfRule type="beginsWith" dxfId="10" priority="22" operator="beginsWith" text="Fission">
       <formula>LEFT(H3,LEN("Fission"))="Fission"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="23">
+    <cfRule type="expression" dxfId="9" priority="23">
       <formula>H3="Missing Data"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="24">
+    <cfRule type="expression" dxfId="8" priority="24">
       <formula>H3="Death"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="25">
+    <cfRule type="expression" dxfId="7" priority="25">
       <formula>H3="Shrinkage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="26">
+    <cfRule type="expression" dxfId="6" priority="26">
       <formula>H3="Growth"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="27">
+    <cfRule type="expression" dxfId="5" priority="27">
       <formula>H3="Recruitment"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="beginsWith" dxfId="12" priority="10" operator="beginsWith" text="FI">
+    <cfRule type="beginsWith" dxfId="4" priority="10" operator="beginsWith" text="FI">
       <formula>LEFT(I2,LEN("FI"))="FI"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="Missing data">
+    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Missing data">
       <formula>NOT(ISERROR(SEARCH("Missing data",I2)))</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="10" priority="12" operator="beginsWith" text="R">
+    <cfRule type="beginsWith" dxfId="2" priority="12" operator="beginsWith" text="R">
       <formula>LEFT(I2,LEN("R"))="R"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="NA">
+    <cfRule type="containsText" dxfId="1" priority="13" operator="containsText" text="NA">
       <formula>NOT(ISERROR(SEARCH("NA",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="14" operator="containsText" text="D">
+    <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="D">
       <formula>NOT(ISERROR(SEARCH("D",I2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A34:C34">
-    <cfRule type="expression" dxfId="7" priority="7">
-      <formula>A34="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="8">
-      <formula>A34="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:C35">
-    <cfRule type="expression" dxfId="5" priority="5">
-      <formula>A35="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
-      <formula>A35="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A36:C36">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>A36="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
-      <formula>A36="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A37:C37">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>A37="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>A37="Na"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions gridLines="1"/>
